--- a/backend/excel_data/Employee_Master_Reference_20260707_164120.xlsx
+++ b/backend/excel_data/Employee_Master_Reference_20260707_164120.xlsx
@@ -1677,7 +1677,7 @@
       </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>Karthik Kumar Malapati_ManualTesting_8_Sails Resume.docx</t>
+          <t>KarthikMindi_AutomationTesting_4+_SailsResume.docx</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>Sai Praveen Krishna Pinnamareddy_ReactJS_4_Sails Resume.docx</t>
+          <t>SaiKrishnaKillamsetti_Java_8_Sails_Resume.docx</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="T94" s="9" t="inlineStr">
         <is>
-          <t>Dinesh Kumar Kothapalli_.Net_1_Sails Resume.docx</t>
+          <t>DineshVaranasi_Automation_3_Sails_Resume.docx</t>
         </is>
       </c>
     </row>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="T173" s="7" t="inlineStr">
         <is>
-          <t>Gopi Patchala_React_6_Sails_Resume.docx</t>
+          <t>SatyalaGopi_Java_10_Sails_Resume.docx</t>
         </is>
       </c>
     </row>
@@ -22269,7 +22269,7 @@
       </c>
       <c r="T231" s="7" t="inlineStr">
         <is>
-          <t>SS518_KAVYA_NAMBALLA_Java_AI.docx</t>
+          <t>KAVYABAMMIDI_Angular,AI.docx</t>
         </is>
       </c>
     </row>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="T236" s="9" t="inlineStr">
         <is>
-          <t>Swetha_PHP_10_sails resume.docx</t>
+          <t>SwethaKonkyana_DotNet_AI.docx</t>
         </is>
       </c>
     </row>
